--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-04-2026.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>£81.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>£51.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-04-2026.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£81.55</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£51.2</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-04-2026.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£49.82</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
